--- a/XLibur.Tests/Resource/Examples/Ranges/AddingRowToTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/AddingRowToTables.xlsx
@@ -19,9 +19,27 @@
     <x:t>FName</x:t>
   </x:si>
   <x:si>
+    <x:t>John</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hank</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dagny</x:t>
+  </x:si>
+  <x:si>
     <x:t>LName</x:t>
   </x:si>
   <x:si>
+    <x:t>Galt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rearden</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Taggart</x:t>
+  </x:si>
+  <x:si>
     <x:t>Outcast</x:t>
   </x:si>
   <x:si>
@@ -29,24 +47,6 @@
   </x:si>
   <x:si>
     <x:t>Income</x:t>
-  </x:si>
-  <x:si>
-    <x:t>John</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Galt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hank</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rearden</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dagny</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Taggart</x:t>
   </x:si>
   <x:si>
     <x:t>dummy value</x:t>
@@ -722,24 +722,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E2" s="15" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F2" s="16" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:17">
       <x:c r="B3" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
         <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>6</x:v>
       </x:c>
       <x:c r="D3" s="0" t="b">
         <x:v>1</x:v>
@@ -753,10 +753,10 @@
     </x:row>
     <x:row r="4" spans="1:17">
       <x:c r="B4" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D4" s="0" t="b">
         <x:v>0</x:v>
@@ -770,10 +770,10 @@
     </x:row>
     <x:row r="5" spans="1:17">
       <x:c r="B5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D5" s="0" t="b">
         <x:v>0</x:v>

--- a/XLibur.Tests/Resource/Examples/Ranges/AddingRowToTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/AddingRowToTables.xlsx
@@ -703,28 +703,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:F6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="7.424911" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="8.567768" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.139196" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="8.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.140625"/>
+    <x:col min="2" max="2" width="7.424911" customWidth="1"/>
+    <x:col min="3" max="3" width="8.567768" customWidth="1"/>
+    <x:col min="4" max="4" width="8.139196" customWidth="1"/>
+    <x:col min="5" max="5" width="10.139196" customWidth="1"/>
+    <x:col min="6" max="6" width="8.710625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:17">
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="D2" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="E2" s="15" t="s">
@@ -735,13 +732,13 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:17">
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="C3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="b">
+      <x:c r="D3" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E3" s="15">
@@ -752,13 +749,13 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:17">
-      <x:c r="B4" s="0" t="s">
+      <x:c r="B4" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="C4" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="b">
+      <x:c r="D4" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E4" s="15">
@@ -769,13 +766,13 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:17">
-      <x:c r="B5" s="0" t="s">
+      <x:c r="B5" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="C5" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="b">
+      <x:c r="D5" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E5" s="15">
@@ -790,15 +787,12 @@
       <x:c r="F6" s="16"/>
     </x:row>
     <x:row r="6000" spans="1:17">
-      <x:c r="Q6000" s="0" t="s">
+      <x:c r="Q6000" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId5"/>
   </x:tableParts>

--- a/XLibur.Tests/Resource/Examples/Ranges/AddingRowToTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/AddingRowToTables.xlsx
@@ -707,11 +707,11 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="7.424911" customWidth="1"/>
-    <x:col min="3" max="3" width="8.567768" customWidth="1"/>
-    <x:col min="4" max="4" width="8.139196" customWidth="1"/>
-    <x:col min="5" max="5" width="10.139196" customWidth="1"/>
-    <x:col min="6" max="6" width="8.710625" customWidth="1"/>
+    <x:col min="2" max="2" width="7.139196" customWidth="1"/>
+    <x:col min="3" max="3" width="8.282054" customWidth="1"/>
+    <x:col min="4" max="4" width="7.853482" customWidth="1"/>
+    <x:col min="5" max="5" width="9.853482" customWidth="1"/>
+    <x:col min="6" max="6" width="8.424911" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:17">

--- a/XLibur.Tests/Resource/Examples/Ranges/AddingRowToTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/AddingRowToTables.xlsx
@@ -706,12 +706,12 @@
   <x:dimension ref="A1:F6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="7.139196" customWidth="1"/>
-    <x:col min="3" max="3" width="8.282054" customWidth="1"/>
-    <x:col min="4" max="4" width="7.853482" customWidth="1"/>
-    <x:col min="5" max="5" width="9.853482" customWidth="1"/>
-    <x:col min="6" max="6" width="8.424911" customWidth="1"/>
+    <x:col min="1" max="1" width="9.144286"/>
+    <x:col min="2" max="2" width="7.142857" customWidth="1"/>
+    <x:col min="3" max="3" width="8.285714" customWidth="1"/>
+    <x:col min="4" max="4" width="7.857143" customWidth="1"/>
+    <x:col min="5" max="5" width="9.857143" customWidth="1"/>
+    <x:col min="6" max="6" width="8.428571" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:17">
